--- a/downloads/Pack 925 - Den Planning Grid.xlsx
+++ b/downloads/Pack 925 - Den Planning Grid.xlsx
@@ -969,7 +969,7 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Personal Fitness</t>
+          <t>Outdoor Adventurer</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Citizenship</t>
+          <t>Personal Fitness</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>Duty to God</t>
+          <t>Citizenship &amp; Duty to God</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Outdoor Adventurer</t>
+          <t>Complete - Optional: Knife Safety</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Knife Safety (elective) + Catch-Up</t>
+          <t>Crossed Over - Mentor &amp; Celebrate</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>Personal Fitness</t>
+          <t>Outdoor Adventurer</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
@@ -4422,268 +4422,10 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>Camp Meal Plan and Cook</t>
+          <t>Campout Prep and Patrol Plan</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
-        <is>
-          <t>Personal Fitness 1 (Plan a balanced meal for camping; prepare it using camp gear)</t>
-        </is>
-      </c>
-      <c r="G76" s="13" t="inlineStr">
-        <is>
-          <t>menu planning sheets, pencils, sample camp gear list, camp stove or backpacking stove, fuel handled by adults, cook pot or skillet, utensils, wash station, meal ingredients</t>
-        </is>
-      </c>
-      <c r="H76" s="13" t="inlineStr">
-        <is>
-          <t>Start or continue the 14-day activity tracker.
-Ask parents to review the BSA Annual Health and Medical Record with you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="14" t="inlineStr">
-        <is>
-          <t>Arrow of Light</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>November 2026</t>
-        </is>
-      </c>
-      <c r="C77" s="13" t="inlineStr">
-        <is>
-          <t>Personal Fitness</t>
-        </is>
-      </c>
-      <c r="D77" s="13" t="inlineStr">
-        <is>
-          <t>Thu Nov 19</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
-        <is>
-          <t>Patrol Fitness Challenge</t>
-        </is>
-      </c>
-      <c r="F77" s="13" t="inlineStr">
-        <is>
-          <t>Personal Fitness 2 (Share 14-day activity tracking - if completed)
-Personal Fitness 3 (Active 30 minutes with patrol/another person including stretching and moving)</t>
-        </is>
-      </c>
-      <c r="G77" s="13" t="inlineStr">
-        <is>
-          <t>open space, cones, stopwatch, water access, activity trackers, pencils</t>
-        </is>
-      </c>
-      <c r="H77" s="13" t="inlineStr">
-        <is>
-          <t>Finish the 14-day tracker if needed and share it with the den leader.
-Confirm the health record review is complete.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="14" t="inlineStr">
-        <is>
-          <t>Arrow of Light</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>January 2027</t>
-        </is>
-      </c>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>Citizenship</t>
-        </is>
-      </c>
-      <c r="D78" s="13" t="inlineStr">
-        <is>
-          <t>Thu Jan 7</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>Choose and Plan Service</t>
-        </is>
-      </c>
-      <c r="F78" s="13" t="inlineStr">
-        <is>
-          <t>Citizenship 1 (Identify a service project and use the BSA SAFE Checklist to plan it safely)</t>
-        </is>
-      </c>
-      <c r="G78" s="13" t="inlineStr">
-        <is>
-          <t>project idea list, pencils, planning worksheet, BSA SAFE Checklist copy, chart paper, markers</t>
-        </is>
-      </c>
-      <c r="H78" s="13" t="inlineStr">
-        <is>
-          <t>Share the service date, location, clothing, and permission needs with families.
-Ask families to protect a full two-hour service block or plan make-up service.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="14" t="inlineStr">
-        <is>
-          <t>Arrow of Light</t>
-        </is>
-      </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>January 2027</t>
-        </is>
-      </c>
-      <c r="C79" s="13" t="inlineStr">
-        <is>
-          <t>Citizenship</t>
-        </is>
-      </c>
-      <c r="D79" s="13" t="inlineStr">
-        <is>
-          <t>Thu Jan 21</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="inlineStr">
-        <is>
-          <t>Service Project Work Session</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="inlineStr">
-        <is>
-          <t>Citizenship 2 (Participate in a service project for at least two hours total - complete during project/outing if time requirement is met)</t>
-        </is>
-      </c>
-      <c r="G79" s="13" t="inlineStr">
-        <is>
-          <t>project-specific supplies, work gloves, trash bags or boxes, first-aid kit, water, service hour log, pencils</t>
-        </is>
-      </c>
-      <c r="H79" s="13" t="inlineStr">
-        <is>
-          <t>If you did not reach two service hours, finish approved make-up service before April advancement closeout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t>Arrow of Light</t>
-        </is>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>February 2027</t>
-        </is>
-      </c>
-      <c r="C80" s="13" t="inlineStr">
-        <is>
-          <t>Duty to God</t>
-        </is>
-      </c>
-      <c r="D80" s="13" t="inlineStr">
-        <is>
-          <t>Thu Feb 4</t>
-        </is>
-      </c>
-      <c r="E80" s="13" t="inlineStr">
-        <is>
-          <t>Values and Crisis Helpers</t>
-        </is>
-      </c>
-      <c r="F80" s="13" t="inlineStr">
-        <is>
-          <t>Duty to God 2 (Meet with a representative of a faith-based organization that assists people in crisis regardless of faith - if guest attends tonight)</t>
-        </is>
-      </c>
-      <c r="G80" s="13" t="inlineStr">
-        <is>
-          <t>index cards, pencils, guest/visit confirmation, thank-you card, question cards</t>
-        </is>
-      </c>
-      <c r="H80" s="13" t="inlineStr">
-        <is>
-          <t>Complete the family faith/value discussion (req 1).
-Start thinking about how you practice Duty to God daily (req 3).</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
-        <is>
-          <t>Arrow of Light</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="inlineStr">
-        <is>
-          <t>February 2027</t>
-        </is>
-      </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>Duty to God</t>
-        </is>
-      </c>
-      <c r="D81" s="13" t="inlineStr">
-        <is>
-          <t>Thu Feb 11</t>
-        </is>
-      </c>
-      <c r="E81" s="13" t="inlineStr">
-        <is>
-          <t>Duty in Daily Life</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="inlineStr">
-        <is>
-          <t>Duty to God 2 (Crisis-helping organization discussion/visit wrap-up)
-Duty to God 3 (Discuss what Duty to God means and daily practice - if done with adult leader tonight)</t>
-        </is>
-      </c>
-      <c r="G81" s="13" t="inlineStr">
-        <is>
-          <t>notes from visit/guest, thank-you card, markers</t>
-        </is>
-      </c>
-      <c r="H81" s="13" t="inlineStr">
-        <is>
-          <t>Finish any remaining Duty to God home discussions with a parent/guardian.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr">
-        <is>
-          <t>Arrow of Light</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
-        <is>
-          <t>March 2027</t>
-        </is>
-      </c>
-      <c r="C82" s="13" t="inlineStr">
-        <is>
-          <t>Outdoor Adventurer</t>
-        </is>
-      </c>
-      <c r="D82" s="13" t="inlineStr">
-        <is>
-          <t>Thu Mar 4</t>
-        </is>
-      </c>
-      <c r="E82" s="13" t="inlineStr">
-        <is>
-          <t>Campout Prep and Patrol Plan</t>
-        </is>
-      </c>
-      <c r="F82" s="13" t="inlineStr">
         <is>
           <t>Outdoor Adventurer 1 (Scout Basic Essentials)
 Outdoor Adventurer 2 (What to bring and how to carry it)
@@ -4691,15 +4433,279 @@
 Outdoor Adventurer 4 (Locate camp and campsite on a map)</t>
         </is>
       </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>packing checklist, pencils, sample gear, BSA SAFE Checklist, chart paper, markers, camp map, printed site map or blank paper</t>
+        </is>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t>Start gathering cold-weather layers and sleeping gear for Nov 20-22.
+Turn in any required medical forms/permission for the campout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Arrow of Light</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>Outdoor Adventurer</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>Thu Nov 19</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>Final Prep: Camp Kitchen &amp; Setup Skills</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>Outdoor Adventurer 6 prep (Campsite setup and patrol-gear-first plan - demonstrated at the campout)
+Outdoor Adventurer 7 prep (Food safety and kitchen sanitation - demonstrated at the campout)</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>a tent or two, ground cloth, cones or rope to mark areas, 3 wash bins, biodegradable soap, sanitizer, dish towels, food storage bins</t>
+        </is>
+      </c>
+      <c r="H77" s="13" t="inlineStr">
+        <is>
+          <t>Finish packing for Nov 20-22 using your checklist.
+At the campout: set patrol gear first, keep the kitchen sanitary, and join the Sunday-morning debrief to finish the adventure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Arrow of Light</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>Personal Fitness</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>Thu Jan 7</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>Camp Meal Plan and Cook</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="inlineStr">
+        <is>
+          <t>Personal Fitness 1 (Plan a balanced meal for camping; prepare it using camp gear)</t>
+        </is>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>menu planning sheets, pencils, sample camp gear list, camp stove or backpacking stove, fuel handled by adults, cook pot or skillet, utensils, wash station, meal ingredients</t>
+        </is>
+      </c>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>Start or continue the 14-day activity tracker.
+Ask parents to review the BSA Annual Health and Medical Record with you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Arrow of Light</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>Personal Fitness</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Thu Jan 21</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>Patrol Fitness Challenge</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>Personal Fitness 2 (Share 14-day activity tracking - if completed)
+Personal Fitness 3 (Active 30 minutes with patrol/another person including stretching and moving)</t>
+        </is>
+      </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>open space, cones, stopwatch, water access, activity trackers, pencils</t>
+        </is>
+      </c>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t>Finish the 14-day tracker if needed and share it with the den leader.
+Confirm the health record review is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>Arrow of Light</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Citizenship &amp; Duty to God</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Thu Feb 4</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>Citizenship: Plan &amp; Serve</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>Citizenship 1 (Identify a service project and use the BSA SAFE Checklist to plan it safely)
+Citizenship 2 (Two hours of service total - completed at Scouting for Food Feb 6 &amp; 13 or another approved project)</t>
+        </is>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>BSA SAFE Checklist copy, project idea list, planning worksheet, pencils, service hour log, work gloves, collection bags or boxes</t>
+        </is>
+      </c>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>Protect the Scouting for Food dates (Feb 6 &amp; 13) so everyone reaches two service hours.
+Log service hours in Scoutbook right away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>Arrow of Light</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>Citizenship &amp; Duty to God</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>Thu Feb 11</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>Duty to God: Reverence &amp; Service</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>Duty to God 2 (Meet a representative of a faith-based organization that assists people in crisis regardless of faith - guest or visit)
+Duty to God 1 &amp; 3 wrap-up (family faith/value discussion and daily-practice discussion - completed with parent/guardian or adult leader)</t>
+        </is>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>index cards, pencils, guest/visit confirmation, thank-you card, question cards</t>
+        </is>
+      </c>
+      <c r="H81" s="13" t="inlineStr">
+        <is>
+          <t>Finish the family faith/value discussion (req 1) and the daily-practice discussion (req 3) at home if not done.
+This is the LAST required adventure - confirm all six are recorded in Scoutbook so the Scout is ready to cross over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>Arrow of Light</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>Complete - Optional: Knife Safety</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>Thu Mar 4</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>Knife Rules and Safety Circle (optional)</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>Optional elective - Knife Safety 1 (Rules and promise)
+Knife Safety 2 (Safety circle)
+Knife Safety 3 (Care for and use a knife safely)</t>
+        </is>
+      </c>
       <c r="G82" s="13" t="inlineStr">
         <is>
-          <t>packing checklist, pencils, sample gear, BSA SAFE Checklist, chart paper, markers, camp map, printed site map or blank paper</t>
+          <t>printed Cub Scout Knife Safety Rules, pencils, trainer knives or approved pocketknives, work gloves if desired, clean cloth, small sharpening stone for demo only</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
-          <t>Pack for the March 5-7 spring campout using tonight's checklist.
-Bring weather layers, sleeping gear, water bottle, and any required forms.</t>
+          <t>Tell families whether Scouts may bring an approved pocketknife next time and what supervision rules apply.
+This is enrichment - it also front-loads the Scouts BSA Totin' Chip.</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4722,7 @@
       </c>
       <c r="C83" s="13" t="inlineStr">
         <is>
-          <t>Outdoor Adventurer</t>
+          <t>Complete - Optional: Knife Safety</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
@@ -4726,25 +4732,24 @@
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>Campout Debrief and Outdoor Ethics</t>
+          <t>Whittle a Useful Object (optional)</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>Outdoor Adventurer 5 (Participated in campout - outing)
-Outdoor Adventurer 6 (Campsite setup and patrol gear - outing)
-Outdoor Adventurer 7 (Food safety/kitchen sanitation - outing)
-Outdoor Adventurer 8 (Discuss what went well/differently; Outdoor Code and Leave No Trace Principles for Kids)</t>
+          <t>Optional elective - Knife Safety 4 (Make a useful object)
+Knife Safety 5 (Correct cooking knife; slice, chop, mince)</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>chart paper, markers, service/campout attendance notes, Outdoor Code card, Leave No Trace Principles for Kids cards</t>
+          <t>approved pocketknives, soft wood blanks or sticks, cut-resistant gloves if available, drop cloth, first-aid kit, cutting boards, paring knife, chef's knife, serrated knife, soft foods such as bananas, cucumbers, or herbs, sanitizer and paper towels</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>Air out and store gear. Thank the adult who helped you get to the campout.</t>
+          <t>Keep practicing safe knife habits in your new Scouts BSA troop.
+Ask your troop about earning the Totin' Chip.</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4766,7 @@
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>Knife Safety (elective) + Catch-Up</t>
+          <t>Crossed Over - Mentor &amp; Celebrate</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
@@ -4771,25 +4776,23 @@
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>Knife Rules and Safety Circle</t>
+          <t>Mentor a Younger Den (optional)</t>
         </is>
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>Knife Safety 1 (Read, understand, and promise to follow Cub Scout Knife Safety Rules)
-Knife Safety 2 (Demonstrate knife safety circle)
-Knife Safety 3 (Care for and use a knife safely)</t>
+          <t>No required adventure - leadership/service bonus</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>printed Cub Scout Knife Safety Rules, pencils, trainer knives or approved pocketknives, work gloves if desired, clean cloth, small sharpening stone for demo only</t>
+          <t>chosen station supplies</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
         <is>
-          <t>Tell families whether Scouts may bring an approved pocketknife next time and what supervision rules apply.
-Check Scoutbook for any missing required-adventure items.</t>
+          <t>Keep showing up for your troop first; help the pack when you can.
+Invite your family to the April 29 End-of-Year Awards.</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4809,7 @@
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>Knife Safety (elective) + Catch-Up</t>
+          <t>Crossed Over - Mentor &amp; Celebrate</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
@@ -4816,24 +4819,22 @@
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Whittle a Useful Object and Kitchen Cuts</t>
+          <t>End-of-Year Send-Off (optional)</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>Knife Safety 4 (Use a pocketknife to make a useful object)
-Knife Safety 5 (Choose correct cooking knife and demonstrate slice, chop, mince)</t>
+          <t>No required adventure - celebration</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>approved pocketknives, soft wood blanks or sticks, cut-resistant gloves if available, drop cloth, first-aid kit, cutting boards, paring knife, chef's knife, serrated knife, soft foods such as bananas, cucumbers, or herbs, sanitizer and paper towels</t>
+          <t>awards/certificates from the pack, campfire program</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>Bring any final make-up evidence before the April 29 End-of-Year Awards and crossover.
-Celebrate crossing over - keep practicing safe knife habits in Scouts BSA.</t>
+          <t>Congratulations - you finished Cub Scouting and crossed over! Be Prepared and Do a Good Turn Daily.</t>
         </is>
       </c>
     </row>
@@ -5138,27 +5139,27 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
+          <t>[ ] Outdoor Adventurer</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
           <t>[ ] Personal Fitness</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>[ ] Citizenship</t>
-        </is>
-      </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>[ ] Duty to God</t>
+          <t>[ ] Citizenship &amp; Duty to God</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>[ ] Outdoor Adventurer</t>
+          <t>[ ] Complete - Optional: Knife Safety</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>[ ] Knife Safety (elective) + Catch-Up</t>
+          <t>[ ] Crossed Over - Mentor &amp; Celebrate</t>
         </is>
       </c>
     </row>

--- a/downloads/Pack 925 - Den Planning Grid.xlsx
+++ b/downloads/Pack 925 - Den Planning Grid.xlsx
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Flex Week</t>
+          <t>Flex / Special</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -606,187 +606,214 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Thu Sep 3</t>
+          <t>Thu Aug 27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Thu Sep 17</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Thu Sep 10</t>
+          <t>Thu Aug 20 (New Scout Night)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Thu Sep 24 — Pack Meeting</t>
+          <t>Thu Aug 13 — Welcome Back Party (Pack Meeting)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Thu Oct 1</t>
+          <t>Thu Sep 3</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Thu Oct 15</t>
+          <t>Thu Sep 17</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Thu Oct 22</t>
+          <t>Thu Sep 10</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Thu Oct 29 — Pack Meeting (Halloween theme)</t>
+          <t>Thu Sep 24 — Pack Meeting</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Thu Nov 5</t>
+          <t>Thu Oct 1</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Thu Nov 19</t>
+          <t>Thu Oct 15</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Thu Nov 12</t>
+          <t>Thu Oct 22</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>— — No pack meeting (Thanksgiving week 11/26 is dark)</t>
+          <t>Thu Oct 29 — Pack Meeting (Halloween theme)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>January 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Thu Jan 7</t>
+          <t>Thu Nov 5</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Thu Jan 21</t>
+          <t>Thu Nov 19</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Thu Jan 14</t>
+          <t>Thu Nov 12</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Thu Jan 28 — Pack Meeting</t>
+          <t>— — No pack meeting (Thanksgiving week 11/26 is dark)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>February 2027</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Thu Feb 4</t>
+          <t>Thu Jan 7</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Thu Feb 11</t>
+          <t>Thu Jan 21</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Thu Jan 14</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Thu Feb 25 — Blue &amp; Gold / Pack Meeting (2/18 is dark - intersession)</t>
+          <t>Thu Jan 28 — Pack Meeting</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>February 2027</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Thu Mar 4</t>
+          <t>Thu Feb 4</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Thu Mar 18</t>
+          <t>Thu Feb 11</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Thu Mar 11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Thu Mar 25 — Pack Meeting</t>
+          <t>Thu Feb 25 — Blue &amp; Gold / Pack Meeting (2/18 is dark - intersession)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Thu Mar 4</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Thu Mar 18</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Thu Mar 11</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Thu Mar 25 — Pack Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Thu Apr 8</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Thu Apr 22</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Thu Apr 15</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Thu Apr 29 — End-of-Year Awards &amp; Campfire (rank badges awarded)</t>
         </is>
@@ -806,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -865,257 +892,294 @@
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Bobcat</t>
+          <t>Bobcat Kickoff</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Bobcat</t>
+          <t>Bobcat Kickoff</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Bobcat</t>
+          <t>Bobcat Kickoff</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Bobcat</t>
+          <t>Bobcat Kickoff</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>Bobcat</t>
+          <t>Bobcat Kickoff</t>
         </is>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Bobcat</t>
+          <t>Bobcat Kickoff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Mountain Lion</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Tigers in the Wild</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Paws on the Path</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Bear Habitat</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Webelos Walkabout</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>First Aid</t>
+          <t>Bobcat</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Fun on the Run</t>
+          <t>Mountain Lion</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Tiger Bites</t>
+          <t>Tigers in the Wild</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Running With the Pack</t>
+          <t>Paws on the Path</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Bear Strong</t>
+          <t>Bear Habitat</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Stronger, Faster, Higher</t>
+          <t>Webelos Walkabout</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Outdoor Adventurer</t>
+          <t>First Aid</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>January 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>King of the Jungle</t>
+          <t>Fun on the Run</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Team Tiger</t>
+          <t>Tiger Bites</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Council Fire (Duty to Country)</t>
+          <t>Running With the Pack</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Paws for Action</t>
+          <t>Bear Strong</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>My Family</t>
+          <t>Stronger, Faster, Higher</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Personal Fitness</t>
+          <t>Outdoor Adventurer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>February 2027</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Lion's Roar</t>
+          <t>King of the Jungle</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Tiger's Roar</t>
+          <t>Team Tiger</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Safety in Numbers</t>
+          <t>Council Fire (Duty to Country)</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Standing Tall</t>
+          <t>Paws for Action</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>My Safety</t>
+          <t>My Family</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>Citizenship &amp; Duty to God</t>
+          <t>Personal Fitness</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>February 2027</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Lion's Pride</t>
+          <t>Lion's Roar</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Tiger Circles (Duty to God)</t>
+          <t>Tiger's Roar</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Footsteps (Duty to God)</t>
+          <t>Safety in Numbers</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Standing Tall</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>My Community</t>
+          <t>My Safety</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Complete - Optional: Knife Safety</t>
+          <t>Citizenship &amp; Duty to God</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Lion's Pride</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Tiger Circles (Duty to God)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Footsteps (Duty to God)</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>My Community</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Complete - Optional: Knife Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>On Your Mark (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Tiger Tag (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Race Time (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Baloo the Builder (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Earth Rocks! (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>Crossed Over - Mentor &amp; Celebrate</t>
         </is>
@@ -1135,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1198,84 +1262,86 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Thu Aug 27</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Meet Your Den &amp; Start Bobcat</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat (start): Get to know the members of your den.
+Bobcat (start): First look at the Scout Oath, Scout Law, and Cub Scout sign - completed in September.</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>poster board, markers, tape, printable Scout Oath / Scout Law / Sign cards</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Practice the Cub Scout sign and the Scout Oath and Law at home using the printable cards.
+Remember: every Lion brings an adult partner to every meeting - sign up for a host month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Lion</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 3</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Meet the Den &amp; the Scout Law</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Bobcat 1 (Get to know den members)
 Bobcat 2 (Hear the Scout Law; show being friendly)</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>butcher paper / poster board, washable paint or markers, wet wipes, printed Scout Law card</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Give each family the Protect Your Children booklet (Bobcat req 4).
 Remind parents about the shared-leadership host rotation - sign up for a month.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Lion</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>September 2026</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Bobcat</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>Thu Sep 17</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>Do Your Best!</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>Bobcat 3 (Share a 'Do Your Best' moment)</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>beanbags, bucket, painter's tape for a balance line, chair</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>If a family hasn't finished the Protect Your Children booklet, remind them - it completes Bobcat.</t>
-        </is>
-      </c>
-    </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1284,255 +1350,255 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Thu Sep 17</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Do Your Best!</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat 3 (Share a 'Do Your Best' moment)</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>beanbags, bucket, painter's tape for a balance line, chair</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>If a family hasn't finished the Protect Your Children booklet, remind them - it completes Bobcat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Lion</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Mountain Lion</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 1</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Six Essentials &amp; Staying Safe</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Mountain Lion 1 (Six Essentials)
 Mountain Lion 3 (What S.A.W. means)</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>a full set of the Six Essentials to pass around, a whistle for each Lion (or share a few)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Ask families to bring weather-appropriate shoes/jackets next week for the outdoor walk.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Lion</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Mountain Lion</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 15</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Nature Walk: Natural vs Manmade</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>Mountain Lion 2 (20-min outdoor walk; natural vs manmade)
 Mountain Lion 4 (Common animals: wild vs domestic)</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>the Six Essentials, a nearby safe walking area, a few animal picture cards (optional)</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>Mountain Lion complete! Families can review the animals they saw over dinner.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Lion</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Fun on the Run</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 5</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Food Groups &amp; Clean Hands</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Fun on the Run 1 (Five food groups)
 Fun on the Run 2 (Hand washing; when to wash)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>paper plates, food pictures from magazines/printouts, glue sticks, safety scissors, washable glitter or hand lotion + cinnamon, soap, sink/water access, paper towels</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>Encourage families to let Lions help pick a fruit or veggie at the store.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Lion</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Fun on the Run</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 19</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Move It &amp; Rest It</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>Fun on the Run 3 (Active 20 minutes)
 Fun on the Run 4 (Methods that help you rest)</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>open space/gym, cones, parachute (optional), mats or open floor, calm music (optional)</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>Fun on the Run complete! Suggest a family 'active + rest' evening routine.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Lion</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>King of the Jungle</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 7</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>My Family &amp; My Jobs</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>King of the Jungle 1 (Draw the people you live with)</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>paper, crayons/markers, chart paper, markers</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Home job (req 2) and grandparent/citizenship chat (req 3).
 Ask families to bring one canned good next week for the service project.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Lion</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>January 2027</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>King of the Jungle</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Thu Jan 21</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Service Project: Helping Others</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>King of the Jungle 4 (Participate in a service project)</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>depends on project: canned goods box, cards + markers, or trash bags + gloves</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>King of the Jungle complete! Encourage families to keep their home jobs going.</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
@@ -1541,80 +1607,80 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>King of the Jungle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Thu Jan 21</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Service Project: Helping Others</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>King of the Jungle 4 (Participate in a service project)</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>depends on project: canned goods box, cards + markers, or trash bags + gloves</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>King of the Jungle complete! Encourage families to keep their home jobs going.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Lion</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Lion's Roar</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Thu Feb 4</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Shout, Run, Tell + Getting Help</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Lion's Roar 2 (Demonstrate Shout, Run, Tell)
 Lion's Roar 3 (Access emergency services)</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>toy phones or paper phone cutouts</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>Help your Lion memorize their home address and a parent's phone number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Lion</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>February 2027</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Lion's Roar</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Thu Feb 11</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Street &amp; Parking-Lot Smarts</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Lion's Roar 4 (Safely cross a street / walk in a parking lot)</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>painter's tape, a couple of toy cars (optional)</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>Lion's Roar complete! Practice safe crossing on your next real walk.</t>
         </is>
       </c>
     </row>
@@ -1626,37 +1692,37 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>February 2027</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Lion's Pride</t>
+          <t>Lion's Roar</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Thu Mar 4</t>
+          <t>Thu Feb 11</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Cheerful Cards for People We Love</t>
+          <t>Street &amp; Parking-Lot Smarts</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>Lion's Pride 3 (Make and give a cheerful card/drawing)</t>
+          <t>Lion's Roar 4 (Safely cross a street / walk in a parking lot)</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>cardstock/construction paper, crayons/markers, stickers, glue</t>
+          <t>painter's tape, a couple of toy cars (optional)</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>Deliver the cheerful card. Do the family faith-tradition talk + drawing (req 1) and attend a service/gathering (req 2).</t>
+          <t>Lion's Roar complete! Practice safe crossing on your next real walk.</t>
         </is>
       </c>
     </row>
@@ -1678,27 +1744,27 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Thu Mar 18</t>
+          <t>Thu Mar 4</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Sharing Our Traditions</t>
+          <t>Cheerful Cards for People We Love</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Lion's Pride wrap-up (share home drawings; celebrate reverence &amp; gratitude)</t>
+          <t>Lion's Pride 3 (Make and give a cheerful card/drawing)</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>the home drawings, table for a 'gallery'</t>
+          <t>cardstock/construction paper, crayons/markers, stickers, glue</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Lion's Pride complete! All six required Lion adventures are now done - rank badge time!</t>
+          <t>Deliver the cheerful card. Do the family faith-tradition talk + drawing (req 1) and attend a service/gathering (req 2).</t>
         </is>
       </c>
     </row>
@@ -1710,716 +1776,846 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Lion's Pride</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Thu Mar 18</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Sharing Our Traditions</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Lion's Pride wrap-up (share home drawings; celebrate reverence &amp; gratitude)</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>the home drawings, table for a 'gallery'</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Lion's Pride complete! All six required Lion adventures are now done - rank badge time!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Lion</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>On Your Mark (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 8</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Games &amp; Obstacle Relay (On Your Mark 1-2)</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>On Your Mark 1 (Play a game with your den)
 On Your Mark 2 (Obstacle course relay)</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>game supplies as needed, cones, beanbags, tape, tunnel or chairs</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>Any Lion missing a required adventure: send a quick make-up activity home.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Lion</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>April 2027</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>On Your Mark (elective) + Catch-Up</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Thu Apr 22</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Box Derby Race (On Your Mark 3)</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>On Your Mark 3 (Build a box derby and race)</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>cardboard boxes/decorations, markers, ribbons for all</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>See you at End-of-Year Awards 4/29 - Lions get their rank badge!</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
+          <t>Lion</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>April 2027</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>On Your Mark (elective) + Catch-Up</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Thu Apr 22</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Box Derby Race (On Your Mark 3)</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>On Your Mark 3 (Build a box derby and race)</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>cardboard boxes/decorations, markers, ribbons for all</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>See you at End-of-Year Awards 4/29 - Lions get their rank badge!</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Thu Aug 27</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Meet Your Den &amp; Start Bobcat</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat (start): Get to know the members of your den.
+Bobcat (start): First look at the Scout Oath, Scout Law, and Cub Scout sign - completed in September.</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>poster board, markers, tape, printable Scout Oath / Scout Law / Sign cards</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>Practice the Cub Scout sign and the Scout Oath and Law at home using the printable cards.
+Remember: every Tiger brings an adult partner to every meeting - sign up for a host month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Tiger</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 3</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Meet the Den &amp; Scout Spirit</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Bobcat 1 (Get to know den members)
 Bobcat 2 (Recite the Scout Oath with adult partners)
 Bobcat 3 (Scout Law: trustworthy, helpful, or friendly)</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>poster board or butcher paper, orange/black paper strips, markers, tape or glue, printed Scout Oath and Scout Law cards</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>Give each family the Protect Your Children booklet link or handout (Bobcat req 6).
 Ask families to sign up for the shared-leadership host rotation.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 17</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Signs, Salutes &amp; Do Your Best</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Bobcat 4 (Cub Scout sign, salute, and handshake; how each is used)
 Bobcat 5 (Share a Do Your Best time)</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>small flag, station signs</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>If a family has not finished the Protect Your Children booklet, remind them that it completes Bobcat.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Tigers in the Wild</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 1</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Six Essentials &amp; Outdoor Code</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Tigers in the Wild 1 (Identify Six Essentials; show what each is for)
 Tigers in the Wild 2 (Learn the Outdoor Code)
 Tigers in the Wild 4 (Common animals; domesticated vs wild; draw favorite animal)</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>a full set of the Six Essentials, whistles, printed Outdoor Code card, animal picture cards, paper, crayons/markers</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>Bring weather-appropriate shoes/jackets and your Six Essentials for the outdoor walk next session.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Tigers in the Wild</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 15</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>20-Minute Outdoor Walk</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Tigers in the Wild 3 (20-minute walk with Six Essentials; natural vs manmade)
 Tigers in the Wild 5 (Find a tree and describe how it is helpful)</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>safe walking route, Six Essentials, attendance list, nearby tree</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>Tigers in the Wild complete! Families can repeat the natural/manmade game on any walk.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Tiger Bites</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 5</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Food Groups &amp; Clean Hands</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Tiger Bites 1 (Identify the five food groups)
 Tiger Bites 2 (Practice hand washing; when to wash)</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>paper plates, food pictures or grocery ads, glue sticks, safety scissors, crayons/markers, washable glitter or hand lotion + cinnamon, soap, sink/water access, paper towels</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>Ask Tigers to help choose one food from each food group at home this week.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Tiger Bites</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 19</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>30 Minutes Active + Sleep Helpers</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>Tiger Bites 3 (Be active for 30 minutes)
 Tiger Bites 4 (Practice methods that help you sleep)</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>open space/gym, cones, beanbags, timer, water break area, mats or open floor, calm music (optional)</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>Tiger Bites complete! Try one sleep helper at bedtime this week.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Team Tiger</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 7</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Rules, Jobs &amp; Team Games</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>Team Tiger 1 (Play a game with rules; discuss why rules matter)
 Team Tiger 2 (Choose and do a job that helps your team)
 Team Tiger 3 (Play a game with at least two teams; good team member discussion)</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>open space, job cards, simple supplies for setup/cleanup, cones, beanbags</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>Ask Tigers to notice one team they are part of this week: family, class, den, or sports team.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Team Tiger</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 21</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Service Project Teamwork</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Team Tiger 4 (Participate in a service project)</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>depends on project: canned goods/bags, cards + markers, donation bins, or trash bags + gloves</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>Team Tiger complete! Keep doing helpful jobs at home and in the den.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Tiger's Roar</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Thu Feb 4</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Shout, Run, Tell + 911</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>Tiger's Roar 2 (Demonstrate Shout, Run, Tell)
 Tiger's Roar 3 (Access emergency services)</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>toy phones or paper phone cutouts, sample address card</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>Finish the Protect Yourself Rules video if not already done.
 Help your Tiger memorize home address and a parent phone number.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Tiger's Roar</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Thu Feb 11</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Lost or Separated Plan</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>Tiger's Roar 4 (What to do if lost or separated)</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>whistles, bright bandanna or cloth, chair or wall to be the 'tree', helper picture cards</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H27" s="13" t="inlineStr">
         <is>
           <t>Tiger's Roar complete! Review your family's plan for stores, parks, and campouts.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Tiger Circles (Duty to God)</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Thu Mar 4</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Kindness in Our Circle</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>Tiger Circles 3 (Carry out an act of kindness)</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>cardstock/construction paper, crayons/markers, stickers, envelopes (optional)</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>Do Tiger Circles 1 and 2 at home: family faith tradition talk/drawing and attend a service or reverent gathering.
 Deliver the kindness card if it was sent home.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Tiger Circles (Duty to God)</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Thu Mar 18</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Family Traditions Gallery</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>Tiger Circles wrap-up (share home drawings; confirm home requirements and kindness act)</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>home drawings, display table, advancement notes/checklist</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H29" s="13" t="inlineStr">
         <is>
           <t>Tiger Circles complete when home requirements are done. Tell the den leader if your family still needs a make-up.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Tiger Tag (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 8</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Active Game &amp; Good Sports</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>Tiger Tag 1 (Play an active game; share why you like it)
 Tiger Tag 3 (Discuss what it means to be a good sport)</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>open space, cones, beanbags or soft ball as needed</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t>If any required adventure is incomplete, send the family a specific make-up task tonight.
 Family option: attend a sporting event for Tiger Tag 4.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Tiger</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Tiger Tag (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 22</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Relay Games &amp; Awards Countdown</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>Tiger Tag 2 (Play a relay game with your den)
 Tiger Tag 4 sent home (Attend a sporting event family option)</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>cones, beanbags, open space, timer (optional), advancement checklist, make-up instruction slips</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr">
         <is>
           <t>See you at End-of-Year Awards 4/29 - Tigers receive rank badges once all required adventures are recorded.
 Family option: attend a sporting event for Tiger Tag 4 if you want to complete the elective fully.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Thu Aug 27</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Meet Your Den &amp; Start Bobcat</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat (start): Get to know the members of your den.
+Bobcat (start): First look at the Scout Oath, Scout Law, and Cub Scout sign - completed in September.</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>poster board, markers, tape, printable Scout Oath / Scout Law / Sign cards</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>Practice the Cub Scout sign and the Scout Oath and Law at home using the printable cards.
+Watch for the weekly meeting reminder and mark the pack calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 3</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Wolf Den Team &amp; Scout Law</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>Bobcat 1 (Get to know den members)
 Bobcat 2 (Recite Scout Oath and Scout Law)
@@ -2427,87 +2623,87 @@
 Bobcat 4 (Create den Code of Conduct)</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>printed Scout Oath and Scout Law cards, Scout Law word cards, poster board, markers, tape</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr">
         <is>
           <t>Send the Protect Your Children booklet link/paper home for the Bobcat home requirement.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 17</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Signs, Salute, Handshake &amp; Do Your Best</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>Bobcat 5 (Cub Scout sign, salute, handshake; how each is used)
 Bobcat 6 (Share a time you demonstrated Do Your Best)</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>three station signs, printed review cards</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t>If the Protect Your Children booklet is not done, finish it at home this week to complete Bobcat.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Paws on the Path</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 1</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>Trail Ready Wolves</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>Paws on the Path 1 (Cub Scout Six Essentials)
 Paws on the Path 2 (Buddy system)
@@ -2515,131 +2711,131 @@
 Paws on the Path 4 (Outdoor Code and Leave No Trace Principles for Kids)</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G35" s="13" t="inlineStr">
         <is>
           <t>water bottle, flashlight, small first-aid kit, trail snack, sun protection, whistle, backpack, buddy name cards (optional), sample shoes/jacket/hat, paper and marker, Outdoor Code/LNT card, scenario cards</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="H35" s="13" t="inlineStr">
         <is>
           <t>Wear closed-toe shoes and weather-appropriate layers for the 30-minute outdoor nature walk next session.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Paws on the Path</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 15</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>30-Minute Nature Walk</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>Paws on the Path 2 (Use buddy system on walk)
 Paws on the Path 3 (Wear appropriate clothes/shoes)
 Paws on the Path 5 (30-minute nature walk; describe four animals)</t>
         </is>
       </c>
-      <c r="G33" s="13" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>safe outdoor route, first-aid kit, water, weather gear, clipboard, pencil, animal picture cards (optional)</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>Paws on the Path complete! Families can repeat the walk and compare animals seen in another season.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Running With the Pack</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 5</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Throw, Catch, Balance</t>
         </is>
       </c>
-      <c r="F34" s="13" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>Running With the Pack 1 (Play catch and step back to improve)
 Running With the Pack 2 (Balance walking forward, backward, sideways)</t>
         </is>
       </c>
-      <c r="G34" s="13" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>soft balls or beanbags, cones, painter's tape, beanbags</t>
         </is>
       </c>
-      <c r="H34" s="13" t="inlineStr">
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>Start the healthy menu and shopping list with family for req 6.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Running With the Pack</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 19</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Movement Skills &amp; Team Game</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>Running With the Pack 3 (Front roll, back roll, frog stand)
 Running With the Pack 4 (Sport/game with good sportsmanship)
@@ -2647,87 +2843,87 @@
 Running With the Pack 6 check-in (Healthy menu and shopping list sent home)</t>
         </is>
       </c>
-      <c r="G35" s="13" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>gym mats or soft carpet, adult spotters, cones, open space, ball, cones or boundary markers</t>
         </is>
       </c>
-      <c r="H35" s="13" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>Turn in or report the healthy menu and shopping list if not already done. Running With the Pack is complete when req 6 is finished.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>Council Fire (Duty to Country)</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 7</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Flag Ceremony &amp; Good Neighbors</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F39" s="13" t="inlineStr">
         <is>
           <t>Council Fire 1 (Care for and fold US flag; participate in flag ceremony)
 Council Fire 2 (Three Scout Law points for being a good neighbor)</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>US flag, flag stand, poster paper, markers</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="H39" s="13" t="inlineStr">
         <is>
           <t>Ask families to save small clean boxes/tubes for next session's model neighborhood.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Council Fire (Duty to Country)</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 21</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Build a Neighborhood &amp; Serve</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>Council Fire 3 (Build a model of your home)
 Council Fire 4 (Create a model of a building you visit)
@@ -2735,215 +2931,215 @@
 Council Fire 6 (Participate in a service project; explain how it helps)</t>
         </is>
       </c>
-      <c r="G37" s="13" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>small boxes, paper, markers, tape, glue sticks, safe scissors, butcher paper, service project supplies: cards or food boxes or gloves/trash bags</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t>Council Fire complete! Families can look for good-neighbor actions during the week.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Safety in Numbers</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>Thu Feb 4</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>Safe Touch &amp; Trusted Adults</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="F41" s="13" t="inlineStr">
         <is>
           <t>Safety in Numbers 2 (Discuss safe touch from the video)
 Safety in Numbers 3 intro (Buddy system review)</t>
         </is>
       </c>
-      <c r="G38" s="13" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>Protect Yourself Rules discussion notes, scenario cards</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr">
+      <c r="H41" s="13" t="inlineStr">
         <is>
           <t>If the Wolf Protect Yourself Rules video is not complete, watch it with parent permission before next session.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>Safety in Numbers</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Thu Feb 11</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>Buddy System &amp; Playground Safety</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>Safety in Numbers 3 (Learn and demonstrate buddy system)
 Safety in Numbers 4 (Review safety rules and demonstrate proper playground equipment use)</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>playground or gym equipment, safety rule cards, playground/gym space, balls if using gym games, paper hazard cards (optional)</t>
         </is>
       </c>
-      <c r="H39" s="13" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>Safety in Numbers complete when the home video is done. Practice buddy checks on family outings.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>Footsteps (Duty to God)</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>Thu Mar 4</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>Kindness in Action</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>Footsteps 3 (Carry out an act of kindness)</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>cardstock, markers, stickers, envelopes or delivery bag</t>
         </is>
       </c>
-      <c r="H40" s="13" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr">
         <is>
           <t>Complete Footsteps 1 and 2 with family if not already done. Bring the craft/art or be ready to tell about it next time.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Footsteps (Duty to God)</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>Thu Mar 18</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>The Boy Who Cried Wolf</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>Footsteps 4 (Listen to/read The Boy Who Cried Wolf; discuss truthfulness)
 Footsteps home check (Family traditions craft/service sent home)</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>copy of The Boy Who Cried Wolf, scenario cards, table for home crafts/art</t>
         </is>
       </c>
-      <c r="H41" s="13" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>Footsteps complete when home reqs 1 and 2 are finished. Report completion to the den leader for advancement.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>Race Time (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 8</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>Build, Rules &amp; Speed Ideas</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
+      <c r="F45" s="13" t="inlineStr">
         <is>
           <t>Race Time 1 check-in (Build vehicle with an adult)
 Race Time 2 (Learn race rules)
@@ -2951,88 +3147,132 @@
 Required adventure catch-up checks</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t>printed pack race rules, sample car or boat, pencils, speed idea cards, advancement checklist, station cards, pens</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
+      <c r="H45" s="13" t="inlineStr">
         <is>
           <t>Finish any missing required adventures before the April 29 End-of-Year Awards. Bring race vehicle next session.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>Race Time (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 22</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>Race Day &amp; Sportsmanship</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>Race Time 4 (Discuss good sportsmanship)
 Race Time 5 (Participate in Pinewood Derby or Raingutter Regatta)
 Final required-adventure catch-up before awards</t>
         </is>
       </c>
-      <c r="G43" s="13" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>Pinewood Derby track or rain gutters, cars or boats, race bracket or heat list, towels for regatta, advancement checklist, Scoutbook access or notes</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t>See you at the April 29 End-of-Year Awards. Bring any final home completion notes before awards night.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Thu Aug 27</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>Meet Your Den &amp; Start Bobcat</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat (start): Get to know the members of your den.
+Bobcat (start): First look at the Scout Oath, Scout Law, and Cub Scout sign - completed in September.</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>poster board, markers, tape, printable Scout Oath / Scout Law / Sign cards</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>Practice the Cub Scout sign and the Scout Oath and Law at home using the printable cards.
+Watch for the weekly meeting reminder and mark the pack calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 3</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>Den Team &amp; Code of Conduct</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>Bobcat 1 (Get to know den members)
 Bobcat 2 (Recite Scout Oath and Scout Law)
@@ -3040,89 +3280,89 @@
 Bobcat 4 (Create a Den Code of Conduct)</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>Scout Oath poster or card, whiteboard or chart paper, markers, poster board, tape</t>
         </is>
       </c>
-      <c r="H44" s="13" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>Send the child-abuse prevention guide home and ask families to report completion.
 Ask each Scout to think of one time they did their best for next meeting.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 17</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>Signs, Denner, and Do Your Best</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>Bobcat 5 (Learn denner position and responsibilities)
 Bobcat 6 (Demonstrate sign, salute, handshake; how each is used)
 Bobcat 7 (Share a 'Do Your Best' time and why it matters)</t>
         </is>
       </c>
-      <c r="G45" s="13" t="inlineStr">
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t>scenario cards, denner cord or simple denner badge (optional)</t>
         </is>
       </c>
-      <c r="H45" s="13" t="inlineStr">
+      <c r="H49" s="13" t="inlineStr">
         <is>
           <t>Confirm the child-abuse prevention guide is complete so Bobcat can be recorded.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>Bear Habitat</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 1</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>Plan the One-Mile Walk</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>Bear Habitat 1 (Prepare Six Essentials and weather-appropriate clothing/shoes)
 Bear Habitat 2 (Know Before You Go - locate and confirm route)
@@ -3132,398 +3372,230 @@
 Bear Habitat 8 (Be Kind to Other Visitors - identify how)</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>printed maps, markers, clipboard, station signs, trash bag, gloves, phone/printout for fire danger rating</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>Bring comfortable walking shoes, weather layers, water, and the Six Essentials for the one-mile walk.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>Bear Habitat</t>
         </is>
       </c>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 15</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>One-Mile Leave No Trace Walk</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>Bear Habitat 5 (Leave What You Find - pictures or sketches of five things)
 Bear Habitat 7 (Respect Wildlife - identify six signs of mammals/birds/insects/reptiles)
 Bear Habitat 9 (Go on the one-mile walk practicing Leave No Trace)</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>Six Essentials, trash bag, disposable gloves, route map, notebooks or index cards, pencils, camera/phone if allowed</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
+      <c r="H51" s="13" t="inlineStr">
         <is>
           <t>Bear Habitat complete if the walk was finished. Check for ticks and refill/clean gear at home.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>Bear Strong</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 5</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>Food Groups and 30-Minute Movement</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>Bear Strong 1 (Sample food from three food groups)
 Bear Strong 2 (Be active 30 minutes including stretching and moving)</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>food samples from 3+ groups, napkins, allergy list, water, sample record cards, open space, cones, jump ropes, timer, painter's tape</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>Review the BSA Annual Health and Medical Record with a parent/guardian before the end of the month.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr">
         <is>
           <t>Bear Strong</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 19</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>Personal Fitness and Relaxation</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="F53" s="13" t="inlineStr">
         <is>
           <t>Bear Strong 3 (Be active 15 minutes with heart, muscle, and flexibility exercises)
 Bear Strong 4 (Do a relaxing activity for 10 minutes)</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>timer, exercise cards, open space, mats or clean floor, calm music (optional)</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="H53" s="13" t="inlineStr">
         <is>
           <t>Bear Strong complete after the health record review is done at home.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>Paws for Action</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 7</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>Flag Skills and Symbols</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F54" s="13" t="inlineStr">
         <is>
           <t>Paws for Action 1 (US flag history, raise/lower, fold, display, etiquette)
 Paws for Action 2 (Identify three US symbols; make a model/art of favorite)</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="G54" s="13" t="inlineStr">
         <is>
           <t>US flag, small flag stand or rope, flag etiquette cards, construction paper, markers, clay or craft sticks, glue, scissors</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
+      <c r="H54" s="13" t="inlineStr">
         <is>
           <t>Ask families to suggest a simple service project or nonprofit the den could support next meeting.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
         <is>
           <t>Paws for Action</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 21</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>Nonprofits and Service Project</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="F55" s="13" t="inlineStr">
         <is>
           <t>Paws for Action 3 (Learn a nonprofit mission, funding, and volunteers)
 Paws for Action 4 (Participate in a service project)</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t>nonprofit fact sheet or website printout, photos if available, project supplies, boxes or bags, labels, gloves if cleaning</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
+      <c r="H55" s="13" t="inlineStr">
         <is>
           <t>Paws for Action complete. Encourage Scouts to tell their family the nonprofit's mission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>February 2027</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>Standing Tall</t>
-        </is>
-      </c>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>Thu Feb 4</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>Personal Space Bubble</t>
-        </is>
-      </c>
-      <c r="F52" s="13" t="inlineStr">
-        <is>
-          <t>Standing Tall 2 (Complete the Personal Space Bubble worksheet)</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>Personal Space Bubble worksheets, pencils, scenario cards</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>Finish the Protect Yourself Rules video and family digital-device policy at home.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>February 2027</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>Standing Tall</t>
-        </is>
-      </c>
-      <c r="D53" s="13" t="inlineStr">
-        <is>
-          <t>Thu Feb 11</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>Safety Gear Lab</t>
-        </is>
-      </c>
-      <c r="F53" s="13" t="inlineStr">
-        <is>
-          <t>Standing Tall 4 (Identify common personal safety gear; list protection; demonstrate proper use)</t>
-        </is>
-      </c>
-      <c r="G53" s="13" t="inlineStr">
-        <is>
-          <t>helmet, safety glasses, dust mask, gloves, closed-toe shoes or boot, chart paper, markers, activity gear samples, bike helmet or tool gloves</t>
-        </is>
-      </c>
-      <c r="H53" s="13" t="inlineStr">
-        <is>
-          <t>Standing Tall complete after the home video and digital-device policy are done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>March 2027</t>
-        </is>
-      </c>
-      <c r="C54" s="13" t="inlineStr">
-        <is>
-          <t>Fellowship</t>
-        </is>
-      </c>
-      <c r="D54" s="13" t="inlineStr">
-        <is>
-          <t>Thu Mar 4</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>Kindness in Action</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="inlineStr">
-        <is>
-          <t>Fellowship 3 (Carry out an act of kindness)</t>
-        </is>
-      </c>
-      <c r="G54" s="13" t="inlineStr">
-        <is>
-          <t>cards or paper, markers, stickers, envelopes or cleanup supplies</t>
-        </is>
-      </c>
-      <c r="H54" s="13" t="inlineStr">
-        <is>
-          <t>Work on Fellowship home requirements 1, 2, and 4 with a parent/guardian. Bring optional craft/art notes next meeting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>March 2027</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="inlineStr">
-        <is>
-          <t>Fellowship</t>
-        </is>
-      </c>
-      <c r="D55" s="13" t="inlineStr">
-        <is>
-          <t>Thu Mar 18</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>Traditions Gallery and Wrap-Up</t>
-        </is>
-      </c>
-      <c r="F55" s="13" t="inlineStr">
-        <is>
-          <t>Fellowship wrap-up (share home learning respectfully; confirm kindness and home tasks)</t>
-        </is>
-      </c>
-      <c r="G55" s="13" t="inlineStr">
-        <is>
-          <t>home projects or notes, table, completion checklist, pencils</t>
-        </is>
-      </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>Fellowship complete when home requirements are done. Send any missing items to the leader before April.</t>
         </is>
       </c>
     </row>
@@ -3535,25 +3607,193 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>Standing Tall</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Thu Feb 4</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>Personal Space Bubble</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="inlineStr">
+        <is>
+          <t>Standing Tall 2 (Complete the Personal Space Bubble worksheet)</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>Personal Space Bubble worksheets, pencils, scenario cards</t>
+        </is>
+      </c>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>Finish the Protect Yourself Rules video and family digital-device policy at home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Standing Tall</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Thu Feb 11</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>Safety Gear Lab</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>Standing Tall 4 (Identify common personal safety gear; list protection; demonstrate proper use)</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>helmet, safety glasses, dust mask, gloves, closed-toe shoes or boot, chart paper, markers, activity gear samples, bike helmet or tool gloves</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>Standing Tall complete after the home video and digital-device policy are done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Thu Mar 4</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>Kindness in Action</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>Fellowship 3 (Carry out an act of kindness)</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>cards or paper, markers, stickers, envelopes or cleanup supplies</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>Work on Fellowship home requirements 1, 2, and 4 with a parent/guardian. Bring optional craft/art notes next meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Thu Mar 18</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>Traditions Gallery and Wrap-Up</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>Fellowship wrap-up (share home learning respectfully; confirm kindness and home tasks)</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>home projects or notes, table, completion checklist, pencils</t>
+        </is>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>Fellowship complete when home requirements are done. Send any missing items to the leader before April.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>Baloo the Builder (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 8</t>
         </is>
       </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>Tool Safety and Practice</t>
         </is>
       </c>
-      <c r="F56" s="13" t="inlineStr">
+      <c r="F60" s="13" t="inlineStr">
         <is>
           <t>Baloo the Builder 1 (Learn basic tools and safe use)
 Baloo the Builder 2 (Practice using four tools)
@@ -3561,176 +3801,220 @@
 Baloo the Builder 4 (Determine tools/materials needed)</t>
         </is>
       </c>
-      <c r="G56" s="13" t="inlineStr">
+      <c r="G60" s="13" t="inlineStr">
         <is>
           <t>tape measures, pencils, sandpaper, scrap wood, screwdrivers, screws, hammers, nails, safety glasses, sample project pictures, planning sheets</t>
         </is>
       </c>
-      <c r="H56" s="13" t="inlineStr">
+      <c r="H60" s="13" t="inlineStr">
         <is>
           <t>Ask families to send any missing advancement make-up proof before the April 29 awards.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>Baloo the Builder (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 22</t>
         </is>
       </c>
-      <c r="E57" s="13" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>Build and Celebrate</t>
         </is>
       </c>
-      <c r="F57" s="13" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>Baloo the Builder 5 (Build your project)
 April catch-up (finish any incomplete required adventures before awards)</t>
         </is>
       </c>
-      <c r="G57" s="13" t="inlineStr">
+      <c r="G61" s="13" t="inlineStr">
         <is>
           <t>project kits or pre-cut wood, sandpaper, screws or nails, screwdrivers, hammers, wood glue, markers or paint, safety glasses, broom, dustpan, trash bag, advancement checklist</t>
         </is>
       </c>
-      <c r="H57" s="13" t="inlineStr">
+      <c r="H61" s="13" t="inlineStr">
         <is>
           <t>See you at the April 29 End-of-Year Awards. Bring any final make-up proof before then.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Thu Aug 27</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>Meet Your Den &amp; Start Bobcat</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat (start): Get to know the members of your den.
+Bobcat (start): First look at the Scout Oath, Scout Law, and Cub Scout sign - completed in September.</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>poster board, markers, tape, printable Scout Oath / Scout Law / Sign cards</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>Practice the Cub Scout sign and the Scout Oath and Law at home using the printable cards.
+Watch for the weekly meeting reminder and mark the pack calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Webelos</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 3</t>
         </is>
       </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>Den Team, Oath, and Law</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
+      <c r="F63" s="13" t="inlineStr">
         <is>
           <t>Bobcat 1 (Get to know den members)
 Bobcat 2 (Recite Scout Oath/Law; describe the three points of the Oath)
 Bobcat 3 (Learn about the Scout Law)</t>
         </is>
       </c>
-      <c r="G58" s="13" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>printed Scout Oath cards, scenario cards, printed Scout Law cards</t>
         </is>
       </c>
-      <c r="H58" s="13" t="inlineStr">
+      <c r="H63" s="13" t="inlineStr">
         <is>
           <t>Finish the Protect Your Children booklet at home if not already complete.
 Practice the Scout Oath and Scout Law once this week without looking.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 17</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>Code of Conduct and Denner Jobs</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>Bobcat 4 (Create a Den Code of Conduct)
 Bobcat 5 (Learn denner responsibilities)
 Bobcat 6 (Demonstrate sign, salute, and handshake; how each is used)</t>
         </is>
       </c>
-      <c r="G59" s="13" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>poster board, markers, tape, denner cord or badge (optional), den code poster</t>
         </is>
       </c>
-      <c r="H59" s="13" t="inlineStr">
+      <c r="H64" s="13" t="inlineStr">
         <is>
           <t>Bobcat is complete when the home booklet is done. Tell families who is first denner and what that Scout should do next meeting.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>Webelos Walkabout</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 1</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>Plan the Walk and First Aid</t>
         </is>
       </c>
-      <c r="F60" s="13" t="inlineStr">
+      <c r="F65" s="13" t="inlineStr">
         <is>
           <t>Webelos Walkabout 1 (Prepare Six Essentials and clothing/shoes)
 Webelos Walkabout 2 (Plan a 2-mile route)
@@ -3739,559 +4023,603 @@
 Webelos Walkabout 5 (First aid demos)</t>
         </is>
       </c>
-      <c r="G60" s="13" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>local map printouts, phone or printed forecast, pencils, highlighters, moleskin or bandages, elastic wrap, sunscreen bottle, water bottle, first-aid kit</t>
         </is>
       </c>
-      <c r="H60" s="13" t="inlineStr">
+      <c r="H65" s="13" t="inlineStr">
         <is>
           <t>Bring Six Essentials, comfortable walking shoes, and weather layers for the Oct 15 2-mile walk.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>Webelos Walkabout</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 15</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>The 2-Mile Walk</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>Webelos Walkabout 6 (Go on the 2-mile walk using Leave No Trace and Outdoor Code)
 Webelos Walkabout 7 (Discuss what went well and what to do differently)</t>
         </is>
       </c>
-      <c r="G61" s="13" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>Six Essentials, route map, first-aid kit, trash bag, notepad, pen</t>
         </is>
       </c>
-      <c r="H61" s="13" t="inlineStr">
+      <c r="H66" s="13" t="inlineStr">
         <is>
           <t>Webelos Walkabout complete! Dry out gear and restock any first-aid supplies used.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="14" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C62" s="13" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>Stronger, Faster, Higher</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 5</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>Balanced Meal Challenge</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>Stronger, Faster, Higher 1 (Plan, cook, and eat a balanced meal with den/family)</t>
         </is>
       </c>
-      <c r="G62" s="13" t="inlineStr">
+      <c r="G67" s="13" t="inlineStr">
         <is>
           <t>menu worksheet, pencils, food group chart, ingredients, plates, napkins, serving utensils, handwashing supplies</t>
         </is>
       </c>
-      <c r="H62" s="13" t="inlineStr">
+      <c r="H67" s="13" t="inlineStr">
         <is>
           <t>Review the BSA Annual Health and Medical Record with a parent or guardian before the next meeting.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="14" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>Stronger, Faster, Higher</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 19</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>Move, Train, Relax</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
         <is>
           <t>Stronger, Faster, Higher 2 (Be active 30 minutes with den/another person)
 Stronger, Faster, Higher 3 (Be active 15 minutes with personal exercises)
 Stronger, Faster, Higher 4 (Do a relaxing activity for 10 minutes)</t>
         </is>
       </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>open space, cones, disc or balls, water, timer, exercise station cards, mats or clean floor</t>
         </is>
       </c>
-      <c r="H63" s="13" t="inlineStr">
+      <c r="H68" s="13" t="inlineStr">
         <is>
           <t>Stronger, Faster, Higher complete when the health record review is done at home.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="C69" s="13" t="inlineStr">
         <is>
           <t>My Family</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 7</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>Kindness in Action</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
+      <c r="F69" s="13" t="inlineStr">
         <is>
           <t>My Family 2 (Carry out an act of kindness)</t>
         </is>
       </c>
-      <c r="G64" s="13" t="inlineStr">
+      <c r="G69" s="13" t="inlineStr">
         <is>
           <t>project choice cards, markers, task list, depends on project: cards, bags, snacks, gloves, or cleanup supplies</t>
         </is>
       </c>
-      <c r="H64" s="13" t="inlineStr">
+      <c r="H69" s="13" t="inlineStr">
         <is>
           <t>Complete My Family home conversations and bring or describe the craft/art/food from your favorite family celebration next meeting.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>My Family</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 21</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>Family Traditions Gallery</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
+      <c r="F70" s="13" t="inlineStr">
         <is>
           <t>My Family wrap-up (share home work; confirm home requirements)</t>
         </is>
       </c>
-      <c r="G65" s="13" t="inlineStr">
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>home crafts/art/photos, gallery labels, advancement checklist, make-up slips</t>
         </is>
       </c>
-      <c r="H65" s="13" t="inlineStr">
+      <c r="H70" s="13" t="inlineStr">
         <is>
           <t>My Family is complete when all home conversations and the kindness act are done.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B71" s="13" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>My Safety</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>Thu Feb 4</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>Hazards and Safe Spaces</t>
         </is>
       </c>
-      <c r="F66" s="13" t="inlineStr">
+      <c r="F71" s="13" t="inlineStr">
         <is>
           <t>My Safety 3 (Identify ways your family keeps home/meeting space safe)</t>
         </is>
       </c>
-      <c r="G66" s="13" t="inlineStr">
+      <c r="G71" s="13" t="inlineStr">
         <is>
           <t>clipboard, safety audit checklist, pencils, empty cleaned containers or printed labels, gloves for demo, magnifying glasses (optional)</t>
         </is>
       </c>
-      <c r="H66" s="13" t="inlineStr">
+      <c r="H71" s="13" t="inlineStr">
         <is>
           <t>Watch the Protect Yourself Rules video and complete the home hazard label check with a parent or guardian.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C72" s="13" t="inlineStr">
         <is>
           <t>My Safety</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>Thu Feb 11</t>
         </is>
       </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
         <is>
           <t>Natural Events Plan</t>
         </is>
       </c>
-      <c r="F67" s="13" t="inlineStr">
+      <c r="F72" s="13" t="inlineStr">
         <is>
           <t>My Safety 4 (Complete Be Prepared for Natural Events worksheet for at least two likely events)</t>
         </is>
       </c>
-      <c r="G67" s="13" t="inlineStr">
+      <c r="G72" s="13" t="inlineStr">
         <is>
           <t>Be Prepared for Natural Events worksheets, pencils, local hazard list, sample emergency kit items, backpack or bin, distractor items</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
+      <c r="H72" s="13" t="inlineStr">
         <is>
           <t>My Safety complete when the home video and hazard check are finished. Review your family emergency plan.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B73" s="13" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C73" s="13" t="inlineStr">
         <is>
           <t>My Community</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D73" s="13" t="inlineStr">
         <is>
           <t>Thu Mar 4</t>
         </is>
       </c>
-      <c r="E68" s="13" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>Voting and Elected Leaders</t>
         </is>
       </c>
-      <c r="F68" s="13" t="inlineStr">
+      <c r="F73" s="13" t="inlineStr">
         <is>
           <t>My Community 1 (Learn majority and plurality voting)
 My Community 2 (Speak with someone elected; discover voting type and why)</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="G73" s="13" t="inlineStr">
         <is>
           <t>poster ballot, markers, calculator (optional), guest chair, prepared question cards, pencils</t>
         </is>
       </c>
-      <c r="H68" s="13" t="inlineStr">
+      <c r="H73" s="13" t="inlineStr">
         <is>
           <t>If no elected guest was available, complete the elected-person interview before session 2.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="14" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>My Community</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>Thu Mar 18</t>
         </is>
       </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>Law Timeline and Service</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr">
+      <c r="F74" s="13" t="inlineStr">
         <is>
           <t>My Community 3 (Federal law timeline with three branches)
 My Community 4 (Participate in a service project)</t>
         </is>
       </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="G74" s="13" t="inlineStr">
         <is>
           <t>timeline cards, poster paper, markers, tape, depends on project: gloves, trash bags, cards, markers, boxes, or donated goods</t>
         </is>
       </c>
-      <c r="H69" s="13" t="inlineStr">
+      <c r="H74" s="13" t="inlineStr">
         <is>
           <t>My Community complete! Turn in any elected-person interview notes if done at home.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B75" s="13" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C75" s="13" t="inlineStr">
         <is>
           <t>Earth Rocks! (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 8</t>
         </is>
       </c>
-      <c r="E70" s="13" t="inlineStr">
+      <c r="E75" s="13" t="inlineStr">
         <is>
           <t>Rock Types and Break-Apart Lab</t>
         </is>
       </c>
-      <c r="F70" s="13" t="inlineStr">
+      <c r="F75" s="13" t="inlineStr">
         <is>
           <t>Earth Rocks! 1 (Examine sedimentary, igneous, metamorphic rocks)
 Earth Rocks! 2 (Find a rock, safely break it apart, examine it)</t>
         </is>
       </c>
-      <c r="G70" s="13" t="inlineStr">
+      <c r="G75" s="13" t="inlineStr">
         <is>
           <t>labeled rock samples, sorting trays, hand lenses, found rocks, safety glasses, cloth or towel, hammer, paper, pencils</t>
         </is>
       </c>
-      <c r="H70" s="13" t="inlineStr">
+      <c r="H75" s="13" t="inlineStr">
         <is>
           <t>Bring any missing required-adventure work next meeting so April can close advancement before awards.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
         <is>
           <t>Webelos</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>Earth Rocks! (elective) + Catch-Up</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 22</t>
         </is>
       </c>
-      <c r="E71" s="13" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>Mohs Tests and Crystal Growing</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr">
+      <c r="F76" s="13" t="inlineStr">
         <is>
           <t>Earth Rocks! 3 (Make mineral test kit and test Mohs hardness)
 Earth Rocks! 4 (Grow a crystal)
 April catch-up (finish incomplete required adventures before awards)</t>
         </is>
       </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>mineral samples, pennies, steel nails, glass tiles, record sheets, pencils, Epsom salt or borax, hot water, jars, pipe cleaners or string, labels, advancement checklist, make-up slips, pen</t>
         </is>
       </c>
-      <c r="H71" s="13" t="inlineStr">
+      <c r="H76" s="13" t="inlineStr">
         <is>
           <t>Bring crystal results or photos and any final make-up sign-offs to the April 29 End-of-Year Awards.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>Thu Aug 27</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>Form the Patrol &amp; Start Bobcat</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>Bobcat (start): Get to know the members of your patrol.
+Bobcat (start): First look at the Scout Oath, Scout Law, and Cub Scout sign - completed in September.</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>whiteboard or chart paper, markers, slips of paper for voting, printable Scout Oath / Scout Law / Sign cards</t>
+        </is>
+      </c>
+      <c r="H77" s="13" t="inlineStr">
+        <is>
+          <t>Practice the Cub Scout sign and the Scout Oath and Law at home using the printable cards.
+Watch for the weekly meeting reminder and mark the pack calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Arrow of Light</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C72" s="13" t="inlineStr">
+      <c r="C78" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 3</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
+      <c r="E78" s="13" t="inlineStr">
         <is>
           <t>Form the Patrol</t>
         </is>
       </c>
-      <c r="F72" s="13" t="inlineStr">
+      <c r="F78" s="13" t="inlineStr">
         <is>
           <t>Bobcat 1 (Patrol method: name, patrol leader, benefits)
 Bobcat 2 (Get to know patrol members)
 Bobcat 4 (Create a Code of Conduct)</t>
         </is>
       </c>
-      <c r="G72" s="13" t="inlineStr">
+      <c r="G78" s="13" t="inlineStr">
         <is>
           <t>ballots or slips of paper, pencils, poster board, markers, tape, index cards</t>
         </is>
       </c>
-      <c r="H72" s="13" t="inlineStr">
+      <c r="H78" s="13" t="inlineStr">
         <is>
           <t>Give families the Protect Your Children booklet link (Bobcat req 8).
 Share the planned troop-visit date and ask families to RSVP.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B79" s="13" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C79" s="13" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D79" s="13" t="inlineStr">
         <is>
           <t>Thu Sep 17</t>
         </is>
       </c>
-      <c r="E73" s="13" t="inlineStr">
+      <c r="E79" s="13" t="inlineStr">
         <is>
           <t>Scouts BSA Basics &amp; Troop Visit</t>
         </is>
       </c>
-      <c r="F73" s="13" t="inlineStr">
+      <c r="F79" s="13" t="inlineStr">
         <is>
           <t>Bobcat 3 (Recite Scout Oath and Scout Law with patrol)
 Bobcat 5 (Scouts BSA sign, salute, handshake)
@@ -4299,133 +4627,133 @@
 Bobcat 7 (Visit a Scouts BSA troop - outing if scheduled this night)</t>
         </is>
       </c>
-      <c r="G73" s="13" t="inlineStr">
+      <c r="G79" s="13" t="inlineStr">
         <is>
           <t>small flag for salute practice, troop visit details, question cards, permission/contact info as needed</t>
         </is>
       </c>
-      <c r="H73" s="13" t="inlineStr">
+      <c r="H79" s="13" t="inlineStr">
         <is>
           <t>Complete the troop visit if not done tonight.
 Finish the Protect Your Children booklet to complete Bobcat.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="14" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C80" s="13" t="inlineStr">
         <is>
           <t>First Aid</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 1</t>
         </is>
       </c>
-      <c r="E74" s="13" t="inlineStr">
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>Hurry Cases and Getting Help</t>
         </is>
       </c>
-      <c r="F74" s="13" t="inlineStr">
+      <c r="F80" s="13" t="inlineStr">
         <is>
           <t>First Aid 2 (What to do if someone needs first aid)
 First Aid 3 (Hurry cases: bleeding, heart attack/sudden cardiac arrest, stopped breathing, stroke, poisoning)
 First Aid 4 (Choking victim)</t>
         </is>
       </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="G80" s="13" t="inlineStr">
         <is>
           <t>scenario cards, disposable gloves, gauze pads, roller bandages, CPR face shield trainer or picture, poison control number card, station signs, choking trainer vest or manikin if available, diagram handout</t>
         </is>
       </c>
-      <c r="H74" s="13" t="inlineStr">
+      <c r="H80" s="13" t="inlineStr">
         <is>
           <t>Watch the Protect Yourself Rules video with parent permission if not already done.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="C75" s="13" t="inlineStr">
+      <c r="C81" s="13" t="inlineStr">
         <is>
           <t>First Aid</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="D81" s="13" t="inlineStr">
         <is>
           <t>Thu Oct 15</t>
         </is>
       </c>
-      <c r="E75" s="13" t="inlineStr">
+      <c r="E81" s="13" t="inlineStr">
         <is>
           <t>Treat, Bandage, and Build a Kit</t>
         </is>
       </c>
-      <c r="F75" s="13" t="inlineStr">
+      <c r="F81" s="13" t="inlineStr">
         <is>
           <t>First Aid 5 (Treat shock)
 First Aid 6 (Cuts/scratches, burns/scalds, bites/stings, nosebleeds)
 First Aid 7 (Make and explain a personal first-aid kit)</t>
         </is>
       </c>
-      <c r="G75" s="13" t="inlineStr">
+      <c r="G81" s="13" t="inlineStr">
         <is>
           <t>adhesive bandages, gauze, medical tape, clean cloths, cold pack, blanket, zip bags or small pouches, gauze pads, antiseptic wipes, disposable gloves, emergency info cards, markers</t>
         </is>
       </c>
-      <c r="H75" s="13" t="inlineStr">
+      <c r="H81" s="13" t="inlineStr">
         <is>
           <t>Put the first-aid kit in your day pack and show a parent how each item is used.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="14" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C76" s="13" t="inlineStr">
+      <c r="C82" s="13" t="inlineStr">
         <is>
           <t>Outdoor Adventurer</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 5</t>
         </is>
       </c>
-      <c r="E76" s="13" t="inlineStr">
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>Campout Prep and Patrol Plan</t>
         </is>
       </c>
-      <c r="F76" s="13" t="inlineStr">
+      <c r="F82" s="13" t="inlineStr">
         <is>
           <t>Outdoor Adventurer 1 (Scout Basic Essentials)
 Outdoor Adventurer 2 (What to bring and how to carry it)
@@ -4433,406 +4761,406 @@
 Outdoor Adventurer 4 (Locate camp and campsite on a map)</t>
         </is>
       </c>
-      <c r="G76" s="13" t="inlineStr">
+      <c r="G82" s="13" t="inlineStr">
         <is>
           <t>packing checklist, pencils, sample gear, BSA SAFE Checklist, chart paper, markers, camp map, printed site map or blank paper</t>
         </is>
       </c>
-      <c r="H76" s="13" t="inlineStr">
+      <c r="H82" s="13" t="inlineStr">
         <is>
           <t>Start gathering cold-weather layers and sleeping gear for Nov 20-22.
 Turn in any required medical forms/permission for the campout.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="14" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr">
+      <c r="B83" s="13" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="C77" s="13" t="inlineStr">
+      <c r="C83" s="13" t="inlineStr">
         <is>
           <t>Outdoor Adventurer</t>
         </is>
       </c>
-      <c r="D77" s="13" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>Thu Nov 19</t>
         </is>
       </c>
-      <c r="E77" s="13" t="inlineStr">
+      <c r="E83" s="13" t="inlineStr">
         <is>
           <t>Final Prep: Camp Kitchen &amp; Setup Skills</t>
         </is>
       </c>
-      <c r="F77" s="13" t="inlineStr">
+      <c r="F83" s="13" t="inlineStr">
         <is>
           <t>Outdoor Adventurer 6 prep (Campsite setup and patrol-gear-first plan - demonstrated at the campout)
 Outdoor Adventurer 7 prep (Food safety and kitchen sanitation - demonstrated at the campout)</t>
         </is>
       </c>
-      <c r="G77" s="13" t="inlineStr">
+      <c r="G83" s="13" t="inlineStr">
         <is>
           <t>a tent or two, ground cloth, cones or rope to mark areas, 3 wash bins, biodegradable soap, sanitizer, dish towels, food storage bins</t>
         </is>
       </c>
-      <c r="H77" s="13" t="inlineStr">
+      <c r="H83" s="13" t="inlineStr">
         <is>
           <t>Finish packing for Nov 20-22 using your checklist.
 At the campout: set patrol gear first, keep the kitchen sanitary, and join the Sunday-morning debrief to finish the adventure.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="14" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C78" s="13" t="inlineStr">
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>Personal Fitness</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 7</t>
         </is>
       </c>
-      <c r="E78" s="13" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>Camp Meal Plan and Cook</t>
         </is>
       </c>
-      <c r="F78" s="13" t="inlineStr">
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>Personal Fitness 1 (Plan a balanced meal for camping; prepare it using camp gear)</t>
         </is>
       </c>
-      <c r="G78" s="13" t="inlineStr">
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>menu planning sheets, pencils, sample camp gear list, camp stove or backpacking stove, fuel handled by adults, cook pot or skillet, utensils, wash station, meal ingredients</t>
         </is>
       </c>
-      <c r="H78" s="13" t="inlineStr">
+      <c r="H84" s="13" t="inlineStr">
         <is>
           <t>Start or continue the 14-day activity tracker.
 Ask parents to review the BSA Annual Health and Medical Record with you.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="14" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B79" s="13" t="inlineStr">
+      <c r="B85" s="13" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="C79" s="13" t="inlineStr">
+      <c r="C85" s="13" t="inlineStr">
         <is>
           <t>Personal Fitness</t>
         </is>
       </c>
-      <c r="D79" s="13" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>Thu Jan 21</t>
         </is>
       </c>
-      <c r="E79" s="13" t="inlineStr">
+      <c r="E85" s="13" t="inlineStr">
         <is>
           <t>Patrol Fitness Challenge</t>
         </is>
       </c>
-      <c r="F79" s="13" t="inlineStr">
+      <c r="F85" s="13" t="inlineStr">
         <is>
           <t>Personal Fitness 2 (Share 14-day activity tracking - if completed)
 Personal Fitness 3 (Active 30 minutes with patrol/another person including stretching and moving)</t>
         </is>
       </c>
-      <c r="G79" s="13" t="inlineStr">
+      <c r="G85" s="13" t="inlineStr">
         <is>
           <t>open space, cones, stopwatch, water access, activity trackers, pencils</t>
         </is>
       </c>
-      <c r="H79" s="13" t="inlineStr">
+      <c r="H85" s="13" t="inlineStr">
         <is>
           <t>Finish the 14-day tracker if needed and share it with the den leader.
 Confirm the health record review is complete.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="C80" s="13" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>Citizenship &amp; Duty to God</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>Thu Feb 4</t>
         </is>
       </c>
-      <c r="E80" s="13" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>Citizenship: Plan &amp; Serve</t>
         </is>
       </c>
-      <c r="F80" s="13" t="inlineStr">
+      <c r="F86" s="13" t="inlineStr">
         <is>
           <t>Citizenship 1 (Identify a service project and use the BSA SAFE Checklist to plan it safely)
 Citizenship 2 (Two hours of service total - completed at Scouting for Food Feb 6 &amp; 13 or another approved project)</t>
         </is>
       </c>
-      <c r="G80" s="13" t="inlineStr">
+      <c r="G86" s="13" t="inlineStr">
         <is>
           <t>BSA SAFE Checklist copy, project idea list, planning worksheet, pencils, service hour log, work gloves, collection bags or boxes</t>
         </is>
       </c>
-      <c r="H80" s="13" t="inlineStr">
+      <c r="H86" s="13" t="inlineStr">
         <is>
           <t>Protect the Scouting for Food dates (Feb 6 &amp; 13) so everyone reaches two service hours.
 Log service hours in Scoutbook right away.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B81" s="13" t="inlineStr">
+      <c r="B87" s="13" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="C81" s="13" t="inlineStr">
+      <c r="C87" s="13" t="inlineStr">
         <is>
           <t>Citizenship &amp; Duty to God</t>
         </is>
       </c>
-      <c r="D81" s="13" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr">
         <is>
           <t>Thu Feb 11</t>
         </is>
       </c>
-      <c r="E81" s="13" t="inlineStr">
+      <c r="E87" s="13" t="inlineStr">
         <is>
           <t>Duty to God: Reverence &amp; Service</t>
         </is>
       </c>
-      <c r="F81" s="13" t="inlineStr">
+      <c r="F87" s="13" t="inlineStr">
         <is>
           <t>Duty to God 2 (Meet a representative of a faith-based organization that assists people in crisis regardless of faith - guest or visit)
 Duty to God 1 &amp; 3 wrap-up (family faith/value discussion and daily-practice discussion - completed with parent/guardian or adult leader)</t>
         </is>
       </c>
-      <c r="G81" s="13" t="inlineStr">
+      <c r="G87" s="13" t="inlineStr">
         <is>
           <t>index cards, pencils, guest/visit confirmation, thank-you card, question cards</t>
         </is>
       </c>
-      <c r="H81" s="13" t="inlineStr">
+      <c r="H87" s="13" t="inlineStr">
         <is>
           <t>Finish the family faith/value discussion (req 1) and the daily-practice discussion (req 3) at home if not done.
 This is the LAST required adventure - confirm all six are recorded in Scoutbook so the Scout is ready to cross over.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
-      <c r="C82" s="13" t="inlineStr">
+      <c r="C88" s="13" t="inlineStr">
         <is>
           <t>Complete - Optional: Knife Safety</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>Thu Mar 4</t>
         </is>
       </c>
-      <c r="E82" s="13" t="inlineStr">
+      <c r="E88" s="13" t="inlineStr">
         <is>
           <t>Knife Rules and Safety Circle (optional)</t>
         </is>
       </c>
-      <c r="F82" s="13" t="inlineStr">
+      <c r="F88" s="13" t="inlineStr">
         <is>
           <t>Optional elective - Knife Safety 1 (Rules and promise)
 Knife Safety 2 (Safety circle)
 Knife Safety 3 (Care for and use a knife safely)</t>
         </is>
       </c>
-      <c r="G82" s="13" t="inlineStr">
+      <c r="G88" s="13" t="inlineStr">
         <is>
           <t>printed Cub Scout Knife Safety Rules, pencils, trainer knives or approved pocketknives, work gloves if desired, clean cloth, small sharpening stone for demo only</t>
         </is>
       </c>
-      <c r="H82" s="13" t="inlineStr">
+      <c r="H88" s="13" t="inlineStr">
         <is>
           <t>Tell families whether Scouts may bring an approved pocketknife next time and what supervision rules apply.
 This is enrichment - it also front-loads the Scouts BSA Totin' Chip.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B83" s="13" t="inlineStr">
+      <c r="B89" s="13" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
-      <c r="C83" s="13" t="inlineStr">
+      <c r="C89" s="13" t="inlineStr">
         <is>
           <t>Complete - Optional: Knife Safety</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D89" s="13" t="inlineStr">
         <is>
           <t>Thu Mar 18</t>
         </is>
       </c>
-      <c r="E83" s="13" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>Whittle a Useful Object (optional)</t>
         </is>
       </c>
-      <c r="F83" s="13" t="inlineStr">
+      <c r="F89" s="13" t="inlineStr">
         <is>
           <t>Optional elective - Knife Safety 4 (Make a useful object)
 Knife Safety 5 (Correct cooking knife; slice, chop, mince)</t>
         </is>
       </c>
-      <c r="G83" s="13" t="inlineStr">
+      <c r="G89" s="13" t="inlineStr">
         <is>
           <t>approved pocketknives, soft wood blanks or sticks, cut-resistant gloves if available, drop cloth, first-aid kit, cutting boards, paring knife, chef's knife, serrated knife, soft foods such as bananas, cucumbers, or herbs, sanitizer and paper towels</t>
         </is>
       </c>
-      <c r="H83" s="13" t="inlineStr">
+      <c r="H89" s="13" t="inlineStr">
         <is>
           <t>Keep practicing safe knife habits in your new Scouts BSA troop.
 Ask your troop about earning the Totin' Chip.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="14" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C84" s="13" t="inlineStr">
+      <c r="C90" s="13" t="inlineStr">
         <is>
           <t>Crossed Over - Mentor &amp; Celebrate</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D90" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 8</t>
         </is>
       </c>
-      <c r="E84" s="13" t="inlineStr">
+      <c r="E90" s="13" t="inlineStr">
         <is>
           <t>Mentor a Younger Den (optional)</t>
         </is>
       </c>
-      <c r="F84" s="13" t="inlineStr">
+      <c r="F90" s="13" t="inlineStr">
         <is>
           <t>No required adventure - leadership/service bonus</t>
         </is>
       </c>
-      <c r="G84" s="13" t="inlineStr">
+      <c r="G90" s="13" t="inlineStr">
         <is>
           <t>chosen station supplies</t>
         </is>
       </c>
-      <c r="H84" s="13" t="inlineStr">
+      <c r="H90" s="13" t="inlineStr">
         <is>
           <t>Keep showing up for your troop first; help the pack when you can.
 Invite your family to the April 29 End-of-Year Awards.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="14" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
         <is>
           <t>Arrow of Light</t>
         </is>
       </c>
-      <c r="B85" s="13" t="inlineStr">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
-      <c r="C85" s="13" t="inlineStr">
+      <c r="C91" s="13" t="inlineStr">
         <is>
           <t>Crossed Over - Mentor &amp; Celebrate</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="D91" s="13" t="inlineStr">
         <is>
           <t>Thu Apr 22</t>
         </is>
       </c>
-      <c r="E85" s="13" t="inlineStr">
+      <c r="E91" s="13" t="inlineStr">
         <is>
           <t>End-of-Year Send-Off (optional)</t>
         </is>
       </c>
-      <c r="F85" s="13" t="inlineStr">
+      <c r="F91" s="13" t="inlineStr">
         <is>
           <t>No required adventure - celebration</t>
         </is>
       </c>
-      <c r="G85" s="13" t="inlineStr">
+      <c r="G91" s="13" t="inlineStr">
         <is>
           <t>awards/certificates from the pack, campfire program</t>
         </is>
       </c>
-      <c r="H85" s="13" t="inlineStr">
+      <c r="H91" s="13" t="inlineStr">
         <is>
           <t>Congratulations - you finished Cub Scouting and crossed over! Be Prepared and Do a Good Turn Daily.</t>
         </is>
@@ -4849,7 +5177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4860,6 +5188,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4877,35 +5206,40 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
@@ -4919,35 +5253,40 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
+          <t>[ ] Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
           <t>[ ] Bobcat</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>[ ] Mountain Lion</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>[ ] Fun on the Run</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>[ ] King of the Jungle</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>[ ] Lion's Roar</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>[ ] Lion's Pride</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>[ ] On Your Mark (elective) + Catch-Up</t>
         </is>
@@ -4961,35 +5300,40 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
+          <t>[ ] Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
           <t>[ ] Bobcat</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>[ ] Tigers in the Wild</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>[ ] Tiger Bites</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>[ ] Team Tiger</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>[ ] Tiger's Roar</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>[ ] Tiger Circles (Duty to God)</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>[ ] Tiger Tag (elective) + Catch-Up</t>
         </is>
@@ -5003,35 +5347,40 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
+          <t>[ ] Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
           <t>[ ] Bobcat</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>[ ] Paws on the Path</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>[ ] Running With the Pack</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>[ ] Council Fire (Duty to Country)</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>[ ] Safety in Numbers</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>[ ] Footsteps (Duty to God)</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>[ ] Race Time (elective) + Catch-Up</t>
         </is>
@@ -5045,35 +5394,40 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
+          <t>[ ] Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
           <t>[ ] Bobcat</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>[ ] Bear Habitat</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>[ ] Bear Strong</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>[ ] Paws for Action</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>[ ] Standing Tall</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>[ ] Fellowship</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>[ ] Baloo the Builder (elective) + Catch-Up</t>
         </is>
@@ -5087,35 +5441,40 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
+          <t>[ ] Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
           <t>[ ] Bobcat</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>[ ] Webelos Walkabout</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>[ ] Stronger, Faster, Higher</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>[ ] My Family</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>[ ] My Safety</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>[ ] My Community</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>[ ] Earth Rocks! (elective) + Catch-Up</t>
         </is>
@@ -5129,35 +5488,40 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
+          <t>[ ] Bobcat Kickoff</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
           <t>[ ] Bobcat</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>[ ] First Aid</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>[ ] Outdoor Adventurer</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>[ ] Personal Fitness</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>[ ] Citizenship &amp; Duty to God</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>[ ] Complete - Optional: Knife Safety</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>[ ] Crossed Over - Mentor &amp; Celebrate</t>
         </is>
@@ -5165,7 +5529,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
